--- a/DataTables/DetailText/剧情/003第一次行医.xlsx
+++ b/DataTables/DetailText/剧情/003第一次行医.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\10094312\Downloads\Doctor\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{198E5340-26EA-4462-96A4-B363D2343E08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{859E8EA9-C5E0-4C87-B784-5CE28E6C12FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1778" yWindow="1778" windowWidth="21600" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="2" r:id="rId1"/>
@@ -20,23 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>StoryID</t>
   </si>
@@ -75,10 +64,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>res://Assets/Portrait/StoryNpc/li_yan_wen/li_yan_wen.png</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>从今天起，你就正式开始给病患诊断开药。记住我教给你的，先把脉确定病性，辩证判断所患何病，再因病开方。如果记不住脉象，药方，就翻翻笔记。好了，病人已经在等着你了，快去吧。</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -89,17 +74,24 @@
   <si>
     <t>第一次行医</t>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>BackgroundPath</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>res://Assets/Background/clinic/autumn.png</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -113,7 +105,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -131,6 +123,13 @@
       <name val="Microsoft YaHei"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -208,7 +207,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -486,21 +485,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="57.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="104.75" style="4" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="8.73046875" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="42.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="104.73046875" style="4" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -523,15 +523,18 @@
         <v>4</v>
       </c>
       <c r="H1" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" s="8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="33">
+    <row r="2" spans="1:9" ht="30">
       <c r="A2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>13</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>14</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
@@ -545,14 +548,15 @@
       <c r="F2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="10" t="s">
-        <v>12</v>
-      </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:9">
       <c r="A3" s="5"/>
       <c r="B3" s="7"/>
       <c r="C3" s="1"/>
@@ -560,9 +564,10 @@
       <c r="E3" s="1"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
-      <c r="H3" s="1"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="1"/>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:9">
       <c r="A4" s="5"/>
       <c r="B4" s="7"/>
       <c r="C4" s="1"/>
@@ -570,9 +575,10 @@
       <c r="E4" s="1"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
-      <c r="H4" s="1"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="1"/>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:9">
       <c r="A5" s="5"/>
       <c r="B5" s="7"/>
       <c r="C5" s="1"/>
@@ -580,9 +586,10 @@
       <c r="E5" s="1"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
-      <c r="H5" s="1"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:9">
       <c r="A6" s="5"/>
       <c r="B6" s="7"/>
       <c r="C6" s="1"/>
@@ -590,9 +597,10 @@
       <c r="E6" s="1"/>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-      <c r="H6" s="1"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="1"/>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:9">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="3"/>
@@ -601,6 +609,7 @@
       <c r="F7" s="2"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/003第一次行医.xlsx
+++ b/DataTables/DetailText/剧情/003第一次行医.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{859E8EA9-C5E0-4C87-B784-5CE28E6C12FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2E5E338-A689-4D13-9170-0A082052CD43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1778" yWindow="1778" windowWidth="21600" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="2" r:id="rId1"/>
@@ -20,6 +20,17 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -80,7 +91,8 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>res://Assets/Background/clinic/autumn.png</t>
+    <t>res://Assets/Background/clinic/spring.png</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -91,7 +103,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -105,7 +117,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -126,7 +138,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -207,7 +219,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -488,15 +500,15 @@
   <dimension ref="A1:I7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="42.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="104.73046875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="8.75" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="42.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="104.75" style="4" customWidth="1"/>
     <col min="10" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -529,7 +541,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="30">
+    <row r="2" spans="1:9" ht="33">
       <c r="A2" s="7" t="s">
         <v>12</v>
       </c>

--- a/DataTables/DetailText/剧情/003第一次行医.xlsx
+++ b/DataTables/DetailText/剧情/003第一次行医.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2E5E338-A689-4D13-9170-0A082052CD43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4983D7F0-6EDE-4577-AB3F-7A3B214D13E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/DataTables/DetailText/剧情/003第一次行医.xlsx
+++ b/DataTables/DetailText/剧情/003第一次行医.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4983D7F0-6EDE-4577-AB3F-7A3B214D13E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EACFD2D-D7C9-440D-A022-178290231DCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3075" yWindow="3540" windowWidth="18900" windowHeight="10965" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="2" r:id="rId1"/>

--- a/DataTables/DetailText/剧情/003第一次行医.xlsx
+++ b/DataTables/DetailText/剧情/003第一次行医.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EACFD2D-D7C9-440D-A022-178290231DCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{242778B8-BA9E-4926-9836-9066667F2F2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3075" yWindow="3540" windowWidth="18900" windowHeight="10965" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>StoryID</t>
   </si>
@@ -92,6 +92,10 @@
   </si>
   <si>
     <t>res://Assets/Background/clinic/spring.png</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Hide</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -497,7 +501,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="8.75" style="4" bestFit="1" customWidth="1"/>
@@ -507,12 +511,13 @@
     <col min="5" max="5" width="9.375" style="4" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.625" style="4" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="42.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="104.75" style="4" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="4"/>
+    <col min="8" max="8" width="6.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="42.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="104.75" style="4" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -534,14 +539,17 @@
       <c r="G1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="J1" s="8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="33">
+    <row r="2" spans="1:10" ht="33">
       <c r="A2" s="7" t="s">
         <v>12</v>
       </c>
@@ -561,14 +569,15 @@
         <v>9</v>
       </c>
       <c r="G2" s="2"/>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="2"/>
+      <c r="I2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="J2" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:10">
       <c r="A3" s="5"/>
       <c r="B3" s="7"/>
       <c r="C3" s="1"/>
@@ -577,9 +586,10 @@
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
-      <c r="I3" s="1"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="1"/>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:10">
       <c r="A4" s="5"/>
       <c r="B4" s="7"/>
       <c r="C4" s="1"/>
@@ -588,9 +598,10 @@
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
-      <c r="I4" s="1"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="1"/>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:10">
       <c r="A5" s="5"/>
       <c r="B5" s="7"/>
       <c r="C5" s="1"/>
@@ -599,9 +610,10 @@
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
-      <c r="I5" s="1"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="1"/>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:10">
       <c r="A6" s="5"/>
       <c r="B6" s="7"/>
       <c r="C6" s="1"/>
@@ -610,9 +622,10 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
-      <c r="I6" s="1"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="1"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:10">
       <c r="A7" s="6"/>
       <c r="B7" s="6"/>
       <c r="C7" s="3"/>
@@ -622,6 +635,7 @@
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/003第一次行医.xlsx
+++ b/DataTables/DetailText/剧情/003第一次行医.xlsx
@@ -1,42 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{242778B8-BA9E-4926-9836-9066667F2F2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2C9F00E-F7D7-4200-B243-ED3E628E2E37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="sheet1" sheetId="2" r:id="rId1"/>
+    <sheet name="Story" sheetId="3" r:id="rId1"/>
+    <sheet name="StoryLine" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
   <si>
     <t>StoryID</t>
   </si>
@@ -57,10 +47,6 @@
   </si>
   <si>
     <t>dialogue</t>
-  </si>
-  <si>
-    <t>StoryName</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>PortraitSide</t>
@@ -71,43 +57,83 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>BackgroundPath</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hide</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>StoryName</t>
+  </si>
+  <si>
+    <t>TriggerType</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TriggerScene</t>
+  </si>
+  <si>
+    <t>TriggerDay</t>
+  </si>
+  <si>
+    <t>Reputation</t>
+  </si>
+  <si>
+    <t>EntryId</t>
+  </si>
+  <si>
+    <t>NpcID</t>
+  </si>
+  <si>
+    <t>TriggerNpcID</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>PlayOnce</t>
+  </si>
+  <si>
+    <t>ReturnScene</t>
+  </si>
+  <si>
+    <t>SortIndex</t>
+  </si>
+  <si>
+    <t>scene_enter</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>clinic</t>
+  </si>
+  <si>
     <t>李言闻</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
+    <t>res://Assets/Background/clinic/spring.png</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
     <t>从今天起，你就正式开始给病患诊断开药。记住我教给你的，先把脉确定病性，辩证判断所患何病，再因病开方。如果记不住脉象，药方，就翻翻笔记。好了，病人已经在等着你了，快去吧。</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>003</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>第一次行医</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>BackgroundPath</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>res://Assets/Background/clinic/spring.png</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Hide</t>
-    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -121,7 +147,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -142,13 +168,20 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Noto Sans JP"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -158,6 +191,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -189,7 +234,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -197,33 +242,35 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -500,142 +547,173 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
+  <cols>
+    <col min="1" max="1" width="8.46484375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.46484375" customWidth="1"/>
+    <col min="4" max="4" width="14.1328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.86328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.3984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.06640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.59765625" customWidth="1"/>
+    <col min="11" max="11" width="13.53125" customWidth="1"/>
+    <col min="12" max="12" width="10.73046875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="18">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="18">
+      <c r="A2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="1">
+        <v>2</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="18">
+      <c r="C3" s="10"/>
+      <c r="J3" s="11"/>
+    </row>
+    <row r="4" spans="1:12" ht="18">
+      <c r="C4" s="10"/>
+    </row>
+    <row r="5" spans="1:12" ht="18">
+      <c r="C5" s="10"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="42.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="104.75" style="4" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="11.265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.1328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.9296875" style="3" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="8" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="E1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="30">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="9" t="s">
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="33">
-      <c r="A2" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="1">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" s="10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="5"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="1"/>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="5"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="1"/>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="5"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="1"/>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="5"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="1"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>26</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/003第一次行医.xlsx
+++ b/DataTables/DetailText/剧情/003第一次行医.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2C9F00E-F7D7-4200-B243-ED3E628E2E37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C448C4B4-6E5A-498E-87BC-60308D9813E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
   <si>
     <t>StoryID</t>
   </si>
@@ -123,6 +134,10 @@
   </si>
   <si>
     <t>第一次行医</t>
+  </si>
+  <si>
+    <t>dim</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -133,7 +148,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -147,7 +162,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -168,7 +183,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -234,7 +249,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -268,9 +283,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -549,23 +567,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="8.46484375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.46484375" customWidth="1"/>
-    <col min="4" max="4" width="14.1328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.86328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.86328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.3984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.06640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.59765625" customWidth="1"/>
-    <col min="11" max="11" width="13.53125" customWidth="1"/>
-    <col min="12" max="12" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5" customWidth="1"/>
+    <col min="4" max="4" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.625" customWidth="1"/>
+    <col min="11" max="11" width="13.5" customWidth="1"/>
+    <col min="12" max="12" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="18">
+    <row r="1" spans="1:12">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -603,7 +621,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="18">
+    <row r="2" spans="1:12">
       <c r="A2" s="4" t="s">
         <v>27</v>
       </c>
@@ -635,14 +653,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="18">
+    <row r="3" spans="1:12">
       <c r="C3" s="10"/>
       <c r="J3" s="11"/>
     </row>
-    <row r="4" spans="1:12" ht="18">
+    <row r="4" spans="1:12">
       <c r="C4" s="10"/>
     </row>
-    <row r="5" spans="1:12" ht="18">
+    <row r="5" spans="1:12">
       <c r="C5" s="10"/>
     </row>
   </sheetData>
@@ -656,14 +674,14 @@
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.1328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.9296875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="3" customWidth="1"/>
     <col min="9" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
@@ -693,7 +711,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="30">
+    <row r="2" spans="1:8" ht="33">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -707,7 +725,9 @@
         <v>8</v>
       </c>
       <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="F2" s="13" t="s">
+        <v>29</v>
+      </c>
       <c r="G2" s="2" t="s">
         <v>25</v>
       </c>

--- a/DataTables/DetailText/剧情/003第一次行医.xlsx
+++ b/DataTables/DetailText/剧情/003第一次行医.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C448C4B4-6E5A-498E-87BC-60308D9813E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9467EA72-59C6-4081-AAF1-54B9129CF5B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,23 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
   <si>
     <t>StoryID</t>
   </si>
@@ -138,17 +127,20 @@
   <si>
     <t>dim</t>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ClinicNpcPortraitPath</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -162,7 +154,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -183,12 +175,20 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Noto Sans JP"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Noto Sans JP"/>
@@ -272,8 +272,6 @@
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -286,9 +284,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -566,24 +566,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <dimension ref="A1:M5"/>
+  <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5" customWidth="1"/>
-    <col min="4" max="4" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.625" customWidth="1"/>
-    <col min="11" max="11" width="13.5" customWidth="1"/>
-    <col min="12" max="12" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.46484375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.46484375" customWidth="1"/>
+    <col min="4" max="4" width="14.1328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.86328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.3984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.19921875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.59765625" customWidth="1"/>
+    <col min="12" max="12" width="13.46484375" customWidth="1"/>
+    <col min="13" max="13" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13" ht="18">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -596,32 +597,35 @@
       <c r="D1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="13" t="s">
         <v>18</v>
       </c>
       <c r="J1" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="K1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13" ht="18">
       <c r="A2" s="4" t="s">
         <v>27</v>
       </c>
@@ -643,25 +647,26 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
-      <c r="J2" s="1" t="b">
+      <c r="J2" s="2"/>
+      <c r="K2" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L2" s="1">
+      <c r="M2" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
-      <c r="C3" s="10"/>
-      <c r="J3" s="11"/>
+    <row r="3" spans="1:13" ht="18">
+      <c r="C3" s="8"/>
+      <c r="K3" s="9"/>
     </row>
-    <row r="4" spans="1:12">
-      <c r="C4" s="10"/>
+    <row r="4" spans="1:13" ht="18">
+      <c r="C4" s="8"/>
     </row>
-    <row r="5" spans="1:12">
-      <c r="C5" s="10"/>
+    <row r="5" spans="1:13" ht="18">
+      <c r="C5" s="8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
@@ -674,14 +679,14 @@
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.1328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="3" customWidth="1"/>
     <col min="9" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
@@ -711,27 +716,27 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="33">
+    <row r="2" spans="1:8" ht="30">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="10" t="s">
         <v>24</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="2"/>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="12" t="s">
+      <c r="H2" s="10" t="s">
         <v>26</v>
       </c>
     </row>

--- a/DataTables/DetailText/剧情/003第一次行医.xlsx
+++ b/DataTables/DetailText/剧情/003第一次行医.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9467EA72-59C6-4081-AAF1-54B9129CF5B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A748345D-DA78-4136-B14E-3E417AE1D7E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,6 +21,17 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -140,7 +151,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -154,7 +165,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -175,7 +186,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -288,7 +299,7 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -567,24 +578,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="8.46484375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.1328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.46484375" customWidth="1"/>
-    <col min="4" max="4" width="14.1328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.86328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.86328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.3984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5" customWidth="1"/>
+    <col min="4" max="4" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.25" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="23" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.59765625" customWidth="1"/>
-    <col min="12" max="12" width="13.46484375" customWidth="1"/>
-    <col min="13" max="13" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.625" customWidth="1"/>
+    <col min="12" max="12" width="13.5" customWidth="1"/>
+    <col min="13" max="13" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18">
+    <row r="1" spans="1:13">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -625,7 +636,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="18">
+    <row r="2" spans="1:13">
       <c r="A2" s="4" t="s">
         <v>27</v>
       </c>
@@ -658,14 +669,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="18">
+    <row r="3" spans="1:13">
       <c r="C3" s="8"/>
       <c r="K3" s="9"/>
     </row>
-    <row r="4" spans="1:13" ht="18">
+    <row r="4" spans="1:13">
       <c r="C4" s="8"/>
     </row>
-    <row r="5" spans="1:13" ht="18">
+    <row r="5" spans="1:13">
       <c r="C5" s="8"/>
     </row>
   </sheetData>
@@ -679,14 +690,14 @@
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.1328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="41.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="3" customWidth="1"/>
     <col min="9" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
@@ -716,7 +727,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="30">
+    <row r="2" spans="1:8" ht="33">
       <c r="A2" s="1">
         <v>1</v>
       </c>

--- a/DataTables/DetailText/剧情/003第一次行医.xlsx
+++ b/DataTables/DetailText/剧情/003第一次行医.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A748345D-DA78-4136-B14E-3E417AE1D7E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21A16998-ED2E-429B-8699-E7A47F5FCC29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
   <si>
     <t>StoryID</t>
   </si>
@@ -141,13 +141,17 @@
   </si>
   <si>
     <t>ClinicNpcPortraitPath</t>
+  </si>
+  <si>
+    <t>TriggerStoryID</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -260,7 +264,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -297,6 +301,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -577,8 +584,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:M5"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <dimension ref="A1:N20"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
@@ -586,16 +593,17 @@
     <col min="4" max="4" width="14.125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.625" customWidth="1"/>
-    <col min="12" max="12" width="13.5" customWidth="1"/>
-    <col min="13" max="13" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.625" customWidth="1"/>
+    <col min="13" max="13" width="13.5" customWidth="1"/>
+    <col min="14" max="14" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -615,28 +623,31 @@
         <v>15</v>
       </c>
       <c r="G1" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="I1" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="J1" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
         <v>27</v>
       </c>
@@ -655,29 +666,78 @@
       <c r="F2" s="1">
         <v>0</v>
       </c>
-      <c r="G2" s="2"/>
+      <c r="G2" s="4"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
-      <c r="K2" s="1" t="b">
+      <c r="K2" s="2"/>
+      <c r="L2" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M2" s="1">
+      <c r="N2" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
       <c r="C3" s="8"/>
-      <c r="K3" s="9"/>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="G3" s="14"/>
+      <c r="L3" s="9"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
       <c r="C4" s="8"/>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="G4" s="14"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
       <c r="C5" s="8"/>
+      <c r="G5" s="14"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G6" s="14"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G7" s="14"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G8" s="14"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G9" s="14"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G10" s="14"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G11" s="14"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G12" s="14"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G13" s="14"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G14" s="14"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G15" s="14"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="G16" s="14"/>
+    </row>
+    <row r="17" spans="7:7" x14ac:dyDescent="0.4">
+      <c r="G17" s="14"/>
+    </row>
+    <row r="18" spans="7:7" x14ac:dyDescent="0.4">
+      <c r="G18" s="14"/>
+    </row>
+    <row r="19" spans="7:7" x14ac:dyDescent="0.4">
+      <c r="G19" s="14"/>
+    </row>
+    <row r="20" spans="7:7" x14ac:dyDescent="0.4">
+      <c r="G20" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
@@ -688,7 +748,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.25" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.5" style="3" bestFit="1" customWidth="1"/>
@@ -701,7 +761,7 @@
     <col min="9" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
@@ -727,7 +787,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="33">
+    <row r="2" spans="1:8" ht="33" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>

--- a/DataTables/DetailText/剧情/003第一次行医.xlsx
+++ b/DataTables/DetailText/剧情/003第一次行医.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21A16998-ED2E-429B-8699-E7A47F5FCC29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B60EAC8-10D4-4AE0-9161-F20B30B4F0AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -587,20 +587,19 @@
   <dimension ref="A1:N20"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5" customWidth="1"/>
-    <col min="4" max="4" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.25" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.625" customWidth="1"/>
-    <col min="13" max="13" width="13.5" customWidth="1"/>
-    <col min="14" max="14" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.4">

--- a/DataTables/DetailText/剧情/003第一次行医.xlsx
+++ b/DataTables/DetailText/剧情/003第一次行医.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B60EAC8-10D4-4AE0-9161-F20B30B4F0AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D304150-AA24-4FAC-827A-AEC35410617F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
   <si>
     <t>StoryID</t>
   </si>
@@ -144,6 +144,10 @@
   </si>
   <si>
     <t>TriggerStoryID</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TriggerCureCount</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -211,7 +215,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -233,6 +237,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -264,7 +274,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -302,6 +312,12 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -584,25 +600,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.25" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -615,38 +632,41 @@
       <c r="D1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="G1" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="H1" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="I1" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="J1" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="K1" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="M1" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="N1" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="M1" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="N1" s="5" t="s">
+      <c r="O1" s="16" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
         <v>27</v>
       </c>
@@ -659,84 +679,85 @@
       <c r="D2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="1">
         <v>2</v>
       </c>
-      <c r="F2" s="1">
+      <c r="G2" s="1">
         <v>0</v>
       </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="2"/>
+      <c r="H2" s="4"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
-      <c r="L2" s="1" t="b">
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="N2" s="1">
+      <c r="O2" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.4">
       <c r="C3" s="8"/>
-      <c r="G3" s="14"/>
-      <c r="L3" s="9"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="H3" s="14"/>
+      <c r="N3" s="9"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.4">
       <c r="C4" s="8"/>
-      <c r="G4" s="14"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="H4" s="14"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.4">
       <c r="C5" s="8"/>
-      <c r="G5" s="14"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G6" s="14"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G7" s="14"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G8" s="14"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G9" s="14"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G10" s="14"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G11" s="14"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G12" s="14"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G13" s="14"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G14" s="14"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G15" s="14"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.4">
-      <c r="G16" s="14"/>
-    </row>
-    <row r="17" spans="7:7" x14ac:dyDescent="0.4">
-      <c r="G17" s="14"/>
-    </row>
-    <row r="18" spans="7:7" x14ac:dyDescent="0.4">
-      <c r="G18" s="14"/>
-    </row>
-    <row r="19" spans="7:7" x14ac:dyDescent="0.4">
-      <c r="G19" s="14"/>
-    </row>
-    <row r="20" spans="7:7" x14ac:dyDescent="0.4">
-      <c r="G20" s="14"/>
+      <c r="H5" s="14"/>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="H6" s="14"/>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="H7" s="14"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="H8" s="14"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="H9" s="14"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="H10" s="14"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="H11" s="14"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="H12" s="14"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="H13" s="14"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="H14" s="14"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="H15" s="14"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="H16" s="14"/>
+    </row>
+    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H17" s="14"/>
+    </row>
+    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H18" s="14"/>
+    </row>
+    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H19" s="14"/>
+    </row>
+    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
+      <c r="H20" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/003第一次行医.xlsx
+++ b/DataTables/DetailText/剧情/003第一次行医.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D304150-AA24-4FAC-827A-AEC35410617F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64AEC4C9-39A6-4D65-8241-70D40E8E517B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4642" yWindow="3188" windowWidth="21601" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,23 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
   <si>
     <t>StoryID</t>
   </si>
@@ -89,12 +78,6 @@
     <t>TriggerDay</t>
   </si>
   <si>
-    <t>Reputation</t>
-  </si>
-  <si>
-    <t>EntryId</t>
-  </si>
-  <si>
     <t>NpcID</t>
   </si>
   <si>
@@ -149,17 +132,33 @@
   <si>
     <t>TriggerCureCount</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reputation</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Experience</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>TriggerReputation</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>TriggerEntryId</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -173,7 +172,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -194,7 +193,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -322,7 +321,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -600,26 +599,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:O20"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:Q20"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.59765625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.86328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.06640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -633,54 +635,60 @@
         <v>13</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F1" s="12" t="s">
         <v>14</v>
       </c>
       <c r="G1" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="J1" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="K1" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="I1" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="J1" s="13" t="s">
+      <c r="O1" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="P1" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="K1" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="L1" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="M1" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="N1" s="16" t="s">
+      <c r="Q1" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="O1" s="16" t="s">
+    </row>
+    <row r="2" spans="1:17">
+      <c r="A2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.4">
-      <c r="A2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F2" s="1">
         <v>2</v>
@@ -694,69 +702,71 @@
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
-      <c r="N2" s="1" t="b">
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="O2" s="1">
+      <c r="Q2" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17">
       <c r="C3" s="8"/>
       <c r="H3" s="14"/>
-      <c r="N3" s="9"/>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.4">
+      <c r="P3" s="9"/>
+    </row>
+    <row r="4" spans="1:17">
       <c r="C4" s="8"/>
       <c r="H4" s="14"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17">
       <c r="C5" s="8"/>
       <c r="H5" s="14"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17">
       <c r="H6" s="14"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17">
       <c r="H7" s="14"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17">
       <c r="H8" s="14"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17">
       <c r="H9" s="14"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17">
       <c r="H10" s="14"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17">
       <c r="H11" s="14"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17">
       <c r="H12" s="14"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17">
       <c r="H13" s="14"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17">
       <c r="H14" s="14"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17">
       <c r="H15" s="14"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17">
       <c r="H16" s="14"/>
     </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="8:8">
       <c r="H17" s="14"/>
     </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="8:8">
       <c r="H18" s="14"/>
     </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="8:8">
       <c r="H19" s="14"/>
     </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="8:8">
       <c r="H20" s="14"/>
     </row>
   </sheetData>
@@ -768,20 +778,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="41.25" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.1328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="41.265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="3" customWidth="1"/>
     <col min="9" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
@@ -807,7 +817,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="30">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -815,20 +825,20 @@
         <v>6</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="11" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/DetailText/剧情/003第一次行医.xlsx
+++ b/DataTables/DetailText/剧情/003第一次行医.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64AEC4C9-39A6-4D65-8241-70D40E8E517B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41A057AC-6407-4E31-97A8-7ACA17957359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4642" yWindow="3188" windowWidth="21601" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
   <si>
     <t>StoryID</t>
   </si>
@@ -127,10 +138,6 @@
   </si>
   <si>
     <t>TriggerStoryID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TriggerCureCount</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -154,11 +161,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -172,7 +179,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -193,7 +200,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -321,7 +328,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -599,29 +606,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:Q20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <dimension ref="A1:P20"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.265625" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.3984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23.86328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.06640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -641,13 +647,13 @@
         <v>14</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H1" s="12" t="s">
         <v>29</v>
       </c>
       <c r="I1" s="12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J1" s="13" t="s">
         <v>15</v>
@@ -655,26 +661,23 @@
       <c r="K1" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="13" t="s">
+      <c r="L1" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="M1" s="15" t="s">
         <v>30</v>
-      </c>
-      <c r="M1" s="15" t="s">
-        <v>28</v>
       </c>
       <c r="N1" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="O1" s="15" t="s">
-        <v>32</v>
+      <c r="O1" s="16" t="s">
+        <v>17</v>
       </c>
       <c r="P1" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q1" s="16" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
         <v>25</v>
       </c>
@@ -703,70 +706,69 @@
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="1" t="b">
+      <c r="O2" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="P2" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C3" s="8"/>
       <c r="H3" s="14"/>
-      <c r="P3" s="9"/>
-    </row>
-    <row r="4" spans="1:17">
+      <c r="O3" s="9"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C4" s="8"/>
       <c r="H4" s="14"/>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C5" s="8"/>
       <c r="H5" s="14"/>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H6" s="14"/>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H7" s="14"/>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H8" s="14"/>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H9" s="14"/>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H10" s="14"/>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H11" s="14"/>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H12" s="14"/>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H13" s="14"/>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H14" s="14"/>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H15" s="14"/>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H16" s="14"/>
     </row>
-    <row r="17" spans="8:8">
+    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H17" s="14"/>
     </row>
-    <row r="18" spans="8:8">
+    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H18" s="14"/>
     </row>
-    <row r="19" spans="8:8">
+    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H19" s="14"/>
     </row>
-    <row r="20" spans="8:8">
+    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H20" s="14"/>
     </row>
   </sheetData>
@@ -778,20 +780,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.1328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="41.265625" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="41.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="3" customWidth="1"/>
     <col min="9" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
@@ -817,7 +819,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="30">
+    <row r="2" spans="1:8" ht="33" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>

--- a/DataTables/DetailText/剧情/003第一次行医.xlsx
+++ b/DataTables/DetailText/剧情/003第一次行医.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41A057AC-6407-4E31-97A8-7ACA17957359}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC006BD6-7F0A-4634-B347-646BB54C34F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4642" yWindow="3188" windowWidth="21601" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,17 +21,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -92,10 +81,6 @@
     <t>NpcID</t>
   </si>
   <si>
-    <t>TriggerNpcID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>PlayOnce</t>
   </si>
   <si>
@@ -155,17 +140,21 @@
   <si>
     <t>TriggerEntryId</t>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Disease</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -179,7 +168,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -200,7 +189,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -328,7 +317,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -607,27 +596,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.46484375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.86328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -641,57 +630,57 @@
         <v>13</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F1" s="12" t="s">
         <v>14</v>
       </c>
       <c r="G1" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="I1" s="12" t="s">
         <v>32</v>
-      </c>
-      <c r="H1" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="I1" s="12" t="s">
-        <v>33</v>
       </c>
       <c r="J1" s="13" t="s">
         <v>15</v>
       </c>
       <c r="K1" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="L1" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="M1" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="N1" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="M1" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="N1" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="O1" s="16" t="s">
-        <v>17</v>
-      </c>
       <c r="P1" s="16" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="18.75">
+      <c r="A2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A2" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F2" s="1">
         <v>2</v>
@@ -713,62 +702,62 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16">
       <c r="C3" s="8"/>
       <c r="H3" s="14"/>
       <c r="O3" s="9"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" ht="18.75">
       <c r="C4" s="8"/>
       <c r="H4" s="14"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" ht="18.75">
       <c r="C5" s="8"/>
       <c r="H5" s="14"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" ht="18.75">
       <c r="H6" s="14"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" ht="18.75">
       <c r="H7" s="14"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16" ht="18.75">
       <c r="H8" s="14"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16" ht="18.75">
       <c r="H9" s="14"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16" ht="18.75">
       <c r="H10" s="14"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16" ht="18.75">
       <c r="H11" s="14"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:16" ht="18.75">
       <c r="H12" s="14"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16" ht="18.75">
       <c r="H13" s="14"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:16" ht="18.75">
       <c r="H14" s="14"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16" ht="18.75">
       <c r="H15" s="14"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:16" ht="18.75">
       <c r="H16" s="14"/>
     </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="8:8" ht="18.75">
       <c r="H17" s="14"/>
     </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="8:8" ht="18.75">
       <c r="H18" s="14"/>
     </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="8:8" ht="18.75">
       <c r="H19" s="14"/>
     </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="8:8">
       <c r="H20" s="14"/>
     </row>
   </sheetData>
@@ -780,20 +769,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="41.25" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.1328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="41.265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="3" customWidth="1"/>
     <col min="9" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
@@ -819,7 +808,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="30">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -827,20 +816,20 @@
         <v>6</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="10" t="s">
         <v>23</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/DetailText/剧情/003第一次行医.xlsx
+++ b/DataTables/DetailText/剧情/003第一次行医.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC006BD6-7F0A-4634-B347-646BB54C34F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36FE97DF-3D24-4038-B74D-F47BE984E68F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4642" yWindow="3188" windowWidth="21601" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -666,7 +666,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="18.75">
+    <row r="2" spans="1:16">
       <c r="A2" s="4" t="s">
         <v>24</v>
       </c>
@@ -685,9 +685,7 @@
       <c r="F2" s="1">
         <v>2</v>
       </c>
-      <c r="G2" s="1">
-        <v>0</v>
-      </c>
+      <c r="G2" s="1"/>
       <c r="H2" s="4"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
@@ -707,54 +705,54 @@
       <c r="H3" s="14"/>
       <c r="O3" s="9"/>
     </row>
-    <row r="4" spans="1:16" ht="18.75">
+    <row r="4" spans="1:16">
       <c r="C4" s="8"/>
       <c r="H4" s="14"/>
     </row>
-    <row r="5" spans="1:16" ht="18.75">
+    <row r="5" spans="1:16">
       <c r="C5" s="8"/>
       <c r="H5" s="14"/>
     </row>
-    <row r="6" spans="1:16" ht="18.75">
+    <row r="6" spans="1:16">
       <c r="H6" s="14"/>
     </row>
-    <row r="7" spans="1:16" ht="18.75">
+    <row r="7" spans="1:16">
       <c r="H7" s="14"/>
     </row>
-    <row r="8" spans="1:16" ht="18.75">
+    <row r="8" spans="1:16">
       <c r="H8" s="14"/>
     </row>
-    <row r="9" spans="1:16" ht="18.75">
+    <row r="9" spans="1:16">
       <c r="H9" s="14"/>
     </row>
-    <row r="10" spans="1:16" ht="18.75">
+    <row r="10" spans="1:16">
       <c r="H10" s="14"/>
     </row>
-    <row r="11" spans="1:16" ht="18.75">
+    <row r="11" spans="1:16">
       <c r="H11" s="14"/>
     </row>
-    <row r="12" spans="1:16" ht="18.75">
+    <row r="12" spans="1:16">
       <c r="H12" s="14"/>
     </row>
-    <row r="13" spans="1:16" ht="18.75">
+    <row r="13" spans="1:16">
       <c r="H13" s="14"/>
     </row>
-    <row r="14" spans="1:16" ht="18.75">
+    <row r="14" spans="1:16">
       <c r="H14" s="14"/>
     </row>
-    <row r="15" spans="1:16" ht="18.75">
+    <row r="15" spans="1:16">
       <c r="H15" s="14"/>
     </row>
-    <row r="16" spans="1:16" ht="18.75">
+    <row r="16" spans="1:16">
       <c r="H16" s="14"/>
     </row>
-    <row r="17" spans="8:8" ht="18.75">
+    <row r="17" spans="8:8">
       <c r="H17" s="14"/>
     </row>
-    <row r="18" spans="8:8" ht="18.75">
+    <row r="18" spans="8:8">
       <c r="H18" s="14"/>
     </row>
-    <row r="19" spans="8:8" ht="18.75">
+    <row r="19" spans="8:8">
       <c r="H19" s="14"/>
     </row>
     <row r="20" spans="8:8">

--- a/DataTables/DetailText/剧情/003第一次行医.xlsx
+++ b/DataTables/DetailText/剧情/003第一次行医.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36FE97DF-3D24-4038-B74D-F47BE984E68F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1888CD35-42CA-4804-859E-F605539358E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="34">
   <si>
     <t>StoryID</t>
   </si>
@@ -105,18 +116,10 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>从今天起，你就正式开始给病患诊断开药。记住我教给你的，先把脉确定病性，辩证判断所患何病，再因病开方。如果记不住脉象，药方，就翻翻笔记。好了，病人已经在等着你了，快去吧。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>003</t>
   </si>
   <si>
     <t>第一次行医</t>
-  </si>
-  <si>
-    <t>dim</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>ClinicNpcPortraitPath</t>
@@ -144,17 +147,25 @@
   <si>
     <t>Disease</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>好了，病人已经在等着你了，快去吧。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>从今天起，你就正式开始给病患治病。记住我教给你的，先把脉确定病性，辩证判断所患何病，再因病开方。如果记不住脉象，药方，就翻翻笔记。</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -168,7 +179,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -189,7 +200,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -317,7 +328,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -596,27 +607,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.265625" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.3984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.46484375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.86328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -636,28 +647,28 @@
         <v>14</v>
       </c>
       <c r="G1" s="12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H1" s="12" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I1" s="12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J1" s="13" t="s">
         <v>15</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L1" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="M1" s="15" t="s">
-        <v>29</v>
-      </c>
       <c r="N1" s="15" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="O1" s="16" t="s">
         <v>16</v>
@@ -666,12 +677,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>19</v>
@@ -700,62 +711,62 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C3" s="8"/>
       <c r="H3" s="14"/>
       <c r="O3" s="9"/>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C4" s="8"/>
       <c r="H4" s="14"/>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C5" s="8"/>
       <c r="H5" s="14"/>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H6" s="14"/>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H7" s="14"/>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H8" s="14"/>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H9" s="14"/>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H10" s="14"/>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H11" s="14"/>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H12" s="14"/>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H13" s="14"/>
     </row>
-    <row r="14" spans="1:16">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H14" s="14"/>
     </row>
-    <row r="15" spans="1:16">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H15" s="14"/>
     </row>
-    <row r="16" spans="1:16">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H16" s="14"/>
     </row>
-    <row r="17" spans="8:8">
+    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H17" s="14"/>
     </row>
-    <row r="18" spans="8:8">
+    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H18" s="14"/>
     </row>
-    <row r="19" spans="8:8">
+    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H19" s="14"/>
     </row>
-    <row r="20" spans="8:8">
+    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H20" s="14"/>
     </row>
   </sheetData>
@@ -766,21 +777,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.1328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="41.265625" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="41.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="3" customWidth="1"/>
     <col min="9" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
@@ -806,7 +817,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="30">
+    <row r="2" spans="1:8" ht="33" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -820,14 +831,32 @@
         <v>8</v>
       </c>
       <c r="E2" s="2"/>
-      <c r="F2" s="11" t="s">
-        <v>26</v>
-      </c>
+      <c r="F2" s="11"/>
       <c r="G2" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>23</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="10" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/DetailText/剧情/003第一次行医.xlsx
+++ b/DataTables/DetailText/剧情/003第一次行医.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1888CD35-42CA-4804-859E-F605539358E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C9A3437-79EF-4821-8C8A-39F5B0781308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14317" yWindow="0" windowWidth="14565" windowHeight="15563" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,17 +21,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -161,11 +150,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -179,7 +168,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -200,7 +189,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -328,7 +317,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -607,27 +596,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.59765625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.46484375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.86328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:16">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -677,7 +666,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:16" ht="18.75">
       <c r="A2" s="4" t="s">
         <v>23</v>
       </c>
@@ -711,62 +700,62 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:16">
       <c r="C3" s="8"/>
       <c r="H3" s="14"/>
       <c r="O3" s="9"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:16" ht="18.75">
       <c r="C4" s="8"/>
       <c r="H4" s="14"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:16" ht="18.75">
       <c r="C5" s="8"/>
       <c r="H5" s="14"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:16" ht="18.75">
       <c r="H6" s="14"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:16" ht="18.75">
       <c r="H7" s="14"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:16" ht="18.75">
       <c r="H8" s="14"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:16" ht="18.75">
       <c r="H9" s="14"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:16" ht="18.75">
       <c r="H10" s="14"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:16" ht="18.75">
       <c r="H11" s="14"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:16" ht="18.75">
       <c r="H12" s="14"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:16" ht="18.75">
       <c r="H13" s="14"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:16" ht="18.75">
       <c r="H14" s="14"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:16" ht="18.75">
       <c r="H15" s="14"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:16" ht="18.75">
       <c r="H16" s="14"/>
     </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="8:8" ht="18.75">
       <c r="H17" s="14"/>
     </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="8:8" ht="18.75">
       <c r="H18" s="14"/>
     </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="8:8" ht="18.75">
       <c r="H19" s="14"/>
     </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="8:8">
       <c r="H20" s="14"/>
     </row>
   </sheetData>
@@ -778,20 +767,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="41.25" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.1328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="41.265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="3" customWidth="1"/>
     <col min="9" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
@@ -817,7 +806,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="30">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -839,7 +828,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>2</v>
       </c>

--- a/DataTables/DetailText/剧情/003第一次行医.xlsx
+++ b/DataTables/DetailText/剧情/003第一次行医.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C9A3437-79EF-4821-8C8A-39F5B0781308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB1E5541-8CA1-448C-A148-FA8563EF4FAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14317" yWindow="0" windowWidth="14565" windowHeight="15563" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,6 +21,17 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -53,10 +64,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>left</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>BackgroundPath</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -143,6 +150,10 @@
   </si>
   <si>
     <t>从今天起，你就正式开始给病患治病。记住我教给你的，先把脉确定病性，辩证判断所患何病，再因病开方。如果记不住脉象，药方，就翻翻笔记。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>mid</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -150,11 +161,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -168,7 +179,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -189,7 +200,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -317,7 +328,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -596,91 +607,91 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.59765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.46484375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.265625" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.3984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.46484375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.86328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="G1" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="K1" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="L1" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="N1" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="O1" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="P1" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="H1" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="I1" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="J1" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="L1" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="M1" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="N1" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="O1" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="P1" s="16" t="s">
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="A2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" ht="18.75">
-      <c r="A2" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="E2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F2" s="1">
         <v>2</v>
@@ -700,62 +711,62 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C3" s="8"/>
       <c r="H3" s="14"/>
       <c r="O3" s="9"/>
     </row>
-    <row r="4" spans="1:16" ht="18.75">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C4" s="8"/>
       <c r="H4" s="14"/>
     </row>
-    <row r="5" spans="1:16" ht="18.75">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
       <c r="C5" s="8"/>
       <c r="H5" s="14"/>
     </row>
-    <row r="6" spans="1:16" ht="18.75">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H6" s="14"/>
     </row>
-    <row r="7" spans="1:16" ht="18.75">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H7" s="14"/>
     </row>
-    <row r="8" spans="1:16" ht="18.75">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H8" s="14"/>
     </row>
-    <row r="9" spans="1:16" ht="18.75">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H9" s="14"/>
     </row>
-    <row r="10" spans="1:16" ht="18.75">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H10" s="14"/>
     </row>
-    <row r="11" spans="1:16" ht="18.75">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H11" s="14"/>
     </row>
-    <row r="12" spans="1:16" ht="18.75">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H12" s="14"/>
     </row>
-    <row r="13" spans="1:16" ht="18.75">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H13" s="14"/>
     </row>
-    <row r="14" spans="1:16" ht="18.75">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H14" s="14"/>
     </row>
-    <row r="15" spans="1:16" ht="18.75">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H15" s="14"/>
     </row>
-    <row r="16" spans="1:16" ht="18.75">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
       <c r="H16" s="14"/>
     </row>
-    <row r="17" spans="8:8" ht="18.75">
+    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H17" s="14"/>
     </row>
-    <row r="18" spans="8:8" ht="18.75">
+    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H18" s="14"/>
     </row>
-    <row r="19" spans="8:8" ht="18.75">
+    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H19" s="14"/>
     </row>
-    <row r="20" spans="8:8">
+    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
       <c r="H20" s="14"/>
     </row>
   </sheetData>
@@ -767,20 +778,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.1328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="41.265625" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="41.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="3" customWidth="1"/>
     <col min="9" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
@@ -797,16 +808,16 @@
         <v>4</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="30">
+    <row r="2" spans="1:8" ht="33" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -814,21 +825,21 @@
         <v>6</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>20</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="11"/>
       <c r="G2" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -836,16 +847,16 @@
         <v>6</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>20</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>33</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="11"/>
       <c r="G3" s="2"/>
       <c r="H3" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/DetailText/剧情/003第一次行医.xlsx
+++ b/DataTables/DetailText/剧情/003第一次行医.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB1E5541-8CA1-448C-A148-FA8563EF4FAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{938A0DC0-FCD9-4196-8427-EC62C4D3BA0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -149,11 +149,33 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>从今天起，你就正式开始给病患治病。记住我教给你的，先把脉确定病性，辩证判断所患何病，再因病开方。如果记不住脉象，药方，就翻翻笔记。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>mid</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>从今天起，你就正式开始给病患治病。记住我教给你的，先把脉确定病性，辨证判断所患何病，再因病开方。如果记不住脉象</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>药方，就翻翻笔记。</t>
+    </r>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -161,7 +183,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -219,6 +241,13 @@
       <name val="Noto Sans JP"/>
       <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="6">
@@ -817,7 +846,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="33" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="35.25" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -828,7 +857,7 @@
         <v>20</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E2" s="2"/>
       <c r="F2" s="11"/>
@@ -836,7 +865,7 @@
         <v>21</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -850,7 +879,7 @@
         <v>20</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="11"/>

--- a/DataTables/DetailText/剧情/003第一次行医.xlsx
+++ b/DataTables/DetailText/剧情/003第一次行医.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{938A0DC0-FCD9-4196-8427-EC62C4D3BA0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E1EE4DC-5C66-48CA-8FE7-C7A40E55C9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14317" yWindow="0" windowWidth="14565" windowHeight="15563" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,26 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="34">
-  <si>
-    <t>StoryID</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="37">
   <si>
     <t>LineIndex</t>
   </si>
@@ -72,33 +58,10 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>StoryName</t>
-  </si>
-  <si>
-    <t>TriggerType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TriggerScene</t>
-  </si>
-  <si>
-    <t>TriggerDay</t>
-  </si>
-  <si>
-    <t>NpcID</t>
-  </si>
-  <si>
     <t>PlayOnce</t>
   </si>
   <si>
-    <t>ReturnScene</t>
-  </si>
-  <si>
     <t>SortIndex</t>
-  </si>
-  <si>
-    <t>scene_enter</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>clinic</t>
@@ -116,33 +79,6 @@
   </si>
   <si>
     <t>第一次行医</t>
-  </si>
-  <si>
-    <t>ClinicNpcPortraitPath</t>
-  </si>
-  <si>
-    <t>TriggerStoryID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Reputation</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Experience</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerReputation</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerEntryId</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Disease</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>好了，病人已经在等着你了，快去吧。</t>
@@ -178,16 +114,101 @@
     </r>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>剧情ID</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>剧情名</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发场景</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发天数</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <r>
+      <t>金</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>钱判定</t>
+    </r>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发金钱</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>名望判定</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发名望</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发条目</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发剧情ID</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>触发治疗结果</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>播放后</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>人物ID</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>疾病</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>人物立绘路径</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>奖励金钱</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>奖励名望</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>奖励心得</t>
+    <phoneticPr fontId="9"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -201,7 +222,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -222,7 +243,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -235,22 +256,36 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Noto Sans JP"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Noto Sans JP"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -265,20 +300,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF92D050"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF200"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -309,7 +346,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -329,9 +366,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -344,20 +378,43 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -635,171 +692,198 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:T20"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.25" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.9296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.06640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
+    <row r="1" spans="1:20" s="19" customFormat="1">
+      <c r="A1" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="L1" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="M1" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="N1" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="O1" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="P1" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q1" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="R1" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="S1" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="T1" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="5" t="s">
+    </row>
+    <row r="2" spans="1:20" s="19" customFormat="1">
+      <c r="A2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="H1" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I1" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="J1" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="L1" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="M1" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="N1" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="O1" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="P1" s="16" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="1">
+      <c r="D2" s="21">
         <v>2</v>
       </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="1" t="b">
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" s="20"/>
+      <c r="N2" s="21"/>
+      <c r="O2" s="21"/>
+      <c r="P2" s="21"/>
+      <c r="Q2" s="21"/>
+      <c r="R2" s="22"/>
+      <c r="S2" s="22" t="b">
         <v>1</v>
       </c>
-      <c r="P2" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C3" s="8"/>
-      <c r="H3" s="14"/>
-      <c r="O3" s="9"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C4" s="8"/>
-      <c r="H4" s="14"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="C5" s="8"/>
-      <c r="H5" s="14"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H6" s="14"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H7" s="14"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H8" s="14"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H9" s="14"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H10" s="14"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H11" s="14"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H12" s="14"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H13" s="14"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H14" s="14"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H15" s="14"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="H16" s="14"/>
-    </row>
-    <row r="17" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H17" s="14"/>
-    </row>
-    <row r="18" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H18" s="14"/>
-    </row>
-    <row r="19" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H19" s="14"/>
-    </row>
-    <row r="20" spans="8:8" x14ac:dyDescent="0.4">
-      <c r="H20" s="14"/>
+      <c r="T2" s="22"/>
+    </row>
+    <row r="3" spans="1:20">
+      <c r="C3" s="7"/>
+      <c r="H3" s="11"/>
+      <c r="O3" s="8"/>
+    </row>
+    <row r="4" spans="1:20" ht="18.75">
+      <c r="C4" s="7"/>
+      <c r="H4" s="11"/>
+    </row>
+    <row r="5" spans="1:20" ht="18.75">
+      <c r="C5" s="7"/>
+      <c r="H5" s="11"/>
+    </row>
+    <row r="6" spans="1:20" ht="18.75">
+      <c r="H6" s="11"/>
+    </row>
+    <row r="7" spans="1:20" ht="18.75">
+      <c r="H7" s="11"/>
+    </row>
+    <row r="8" spans="1:20" ht="18.75">
+      <c r="H8" s="11"/>
+    </row>
+    <row r="9" spans="1:20" ht="18.75">
+      <c r="H9" s="11"/>
+    </row>
+    <row r="10" spans="1:20" ht="18.75">
+      <c r="H10" s="11"/>
+    </row>
+    <row r="11" spans="1:20" ht="18.75">
+      <c r="H11" s="11"/>
+    </row>
+    <row r="12" spans="1:20" ht="18.75">
+      <c r="H12" s="11"/>
+    </row>
+    <row r="13" spans="1:20" ht="18.75">
+      <c r="H13" s="11"/>
+    </row>
+    <row r="14" spans="1:20" ht="18.75">
+      <c r="H14" s="11"/>
+    </row>
+    <row r="15" spans="1:20" ht="18.75">
+      <c r="H15" s="11"/>
+    </row>
+    <row r="16" spans="1:20" ht="18.75">
+      <c r="H16" s="11"/>
+    </row>
+    <row r="17" spans="8:8" ht="18.75">
+      <c r="H17" s="11"/>
+    </row>
+    <row r="18" spans="8:8" ht="18.75">
+      <c r="H18" s="11"/>
+    </row>
+    <row r="19" spans="8:8" ht="18.75">
+      <c r="H19" s="11"/>
+    </row>
+    <row r="20" spans="8:8">
+      <c r="H20" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
+  <dataValidations count="5">
+    <dataValidation type="list" sqref="C2" xr:uid="{8865446E-6FD9-4956-B98A-DCF1ACB864AC}">
+      <formula1>"clinic,night,night_end"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="E2 G2" xr:uid="{5D0E6605-F2B9-4F3D-A88A-3CC98778124E}">
+      <formula1>"≥,≤"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="L2" xr:uid="{216AA9E6-A0D7-4A68-B8BE-4C153AA4B945}">
+      <formula1>"clinic,night,end_game"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="S2" xr:uid="{B0591376-7AD2-410B-B84E-790D95EBA20E}">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="K2" xr:uid="{53CB2AF3-AA2E-4DC5-8CC2-DB0957248D95}">
+      <formula1>"cured,failed"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -807,85 +891,85 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="41.25" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.1328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="41.265625" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="3" customWidth="1"/>
     <col min="9" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="F1" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="35.25" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:8" ht="32.65">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>32</v>
+        <v>5</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>17</v>
       </c>
       <c r="E2" s="2"/>
-      <c r="F2" s="11"/>
+      <c r="F2" s="10"/>
       <c r="G2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+        <v>13</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>32</v>
+        <v>5</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>17</v>
       </c>
       <c r="E3" s="2"/>
-      <c r="F3" s="11"/>
+      <c r="F3" s="10"/>
       <c r="G3" s="2"/>
-      <c r="H3" s="10" t="s">
-        <v>31</v>
+      <c r="H3" s="9" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/DataTables/DetailText/剧情/003第一次行医.xlsx
+++ b/DataTables/DetailText/剧情/003第一次行医.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E1EE4DC-5C66-48CA-8FE7-C7A40E55C9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A399AD9B-33E2-4DBA-AF48-B2A704427D68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14317" yWindow="0" windowWidth="14565" windowHeight="15563" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19740" yWindow="5400" windowWidth="16035" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="38">
   <si>
     <t>LineIndex</t>
   </si>
@@ -199,6 +210,10 @@
     <t>奖励心得</t>
     <phoneticPr fontId="9"/>
   </si>
+  <si>
+    <t>Music</t>
+    <phoneticPr fontId="9"/>
+  </si>
 </sst>
 </file>
 
@@ -208,7 +223,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -222,7 +237,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -243,7 +258,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -346,7 +361,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -412,9 +427,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -693,25 +711,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="7.1328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="7" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.9296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.06640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="19" customFormat="1">
+    <row r="1" spans="1:20" s="19" customFormat="1" ht="18">
       <c r="A1" s="12" t="s">
         <v>19</v>
       </c>
@@ -773,7 +791,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="19" customFormat="1">
+    <row r="2" spans="1:20" s="19" customFormat="1" ht="18">
       <c r="A2" s="4" t="s">
         <v>14</v>
       </c>
@@ -812,54 +830,54 @@
       <c r="H3" s="11"/>
       <c r="O3" s="8"/>
     </row>
-    <row r="4" spans="1:20" ht="18.75">
+    <row r="4" spans="1:20">
       <c r="C4" s="7"/>
       <c r="H4" s="11"/>
     </row>
-    <row r="5" spans="1:20" ht="18.75">
+    <row r="5" spans="1:20">
       <c r="C5" s="7"/>
       <c r="H5" s="11"/>
     </row>
-    <row r="6" spans="1:20" ht="18.75">
+    <row r="6" spans="1:20">
       <c r="H6" s="11"/>
     </row>
-    <row r="7" spans="1:20" ht="18.75">
+    <row r="7" spans="1:20">
       <c r="H7" s="11"/>
     </row>
-    <row r="8" spans="1:20" ht="18.75">
+    <row r="8" spans="1:20">
       <c r="H8" s="11"/>
     </row>
-    <row r="9" spans="1:20" ht="18.75">
+    <row r="9" spans="1:20">
       <c r="H9" s="11"/>
     </row>
-    <row r="10" spans="1:20" ht="18.75">
+    <row r="10" spans="1:20">
       <c r="H10" s="11"/>
     </row>
-    <row r="11" spans="1:20" ht="18.75">
+    <row r="11" spans="1:20">
       <c r="H11" s="11"/>
     </row>
-    <row r="12" spans="1:20" ht="18.75">
+    <row r="12" spans="1:20">
       <c r="H12" s="11"/>
     </row>
-    <row r="13" spans="1:20" ht="18.75">
+    <row r="13" spans="1:20">
       <c r="H13" s="11"/>
     </row>
-    <row r="14" spans="1:20" ht="18.75">
+    <row r="14" spans="1:20">
       <c r="H14" s="11"/>
     </row>
-    <row r="15" spans="1:20" ht="18.75">
+    <row r="15" spans="1:20">
       <c r="H15" s="11"/>
     </row>
-    <row r="16" spans="1:20" ht="18.75">
+    <row r="16" spans="1:20">
       <c r="H16" s="11"/>
     </row>
-    <row r="17" spans="8:8" ht="18.75">
+    <row r="17" spans="8:8">
       <c r="H17" s="11"/>
     </row>
-    <row r="18" spans="8:8" ht="18.75">
+    <row r="18" spans="8:8">
       <c r="H18" s="11"/>
     </row>
-    <row r="19" spans="8:8" ht="18.75">
+    <row r="19" spans="8:8">
       <c r="H19" s="11"/>
     </row>
     <row r="20" spans="8:8">
@@ -890,21 +908,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.1328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="41.265625" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="41.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="3" customWidth="1"/>
     <col min="9" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -929,8 +947,11 @@
       <c r="H1" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="32.65">
+      <c r="I1" s="23" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="35.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -951,8 +972,9 @@
       <c r="H2" s="9" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -971,6 +993,7 @@
       <c r="H3" s="9" t="s">
         <v>16</v>
       </c>
+      <c r="I3" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
